--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="827">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>Salmonella sp identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>17576-0</t>
+  </si>
+  <si>
+    <t>Shigella sp identified in Specimen by Organism specific culture</t>
   </si>
   <si>
     <t>17735-2</t>
@@ -2755,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B384"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5815,15 +5821,23 @@
         <v>790</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>792</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -5850,58 +5864,58 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -5928,98 +5942,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1235,6 +1235,12 @@
     <t>Neisseria gonorrhoeae rRNA [Presence] in Vaginal fluid by NAA with probe detection</t>
   </si>
   <si>
+    <t>539-7</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
+  </si>
+  <si>
     <t>53917-1</t>
   </si>
   <si>
@@ -1275,12 +1281,6 @@
   </si>
   <si>
     <t>Escherichia coli shiga-like toxin identified in Specimen</t>
-  </si>
-  <si>
-    <t>539-7</t>
-  </si>
-  <si>
-    <t>Mycobacterium sp identified in Sputum by Organism specific culture</t>
   </si>
   <si>
     <t>540-5</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="849">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,6 +155,12 @@
     <t>Legionella sp DNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>101298-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Throat by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>101307-7</t>
   </si>
   <si>
@@ -281,6 +287,18 @@
     <t>Shigella species+EIEC invasion plasmid antigen H ipaH gene [Presence] in Specimen</t>
   </si>
   <si>
+    <t>105211-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchial specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>105231-5</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Sputum by NAA with probe detection</t>
+  </si>
+  <si>
     <t>105640-7</t>
   </si>
   <si>
@@ -299,6 +317,18 @@
     <t>Tick-borne encephalitis virus Ab [Interpretation] in Serum or Plasma</t>
   </si>
   <si>
+    <t>108111-6</t>
+  </si>
+  <si>
+    <t>Hantavirus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>111556-7</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar aspirate by NAA with non-probe detection</t>
+  </si>
+  <si>
     <t>11259-9</t>
   </si>
   <si>
@@ -893,6 +923,12 @@
     <t>Influenza virus B RNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>40988-8</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>41216-3</t>
   </si>
   <si>
@@ -1697,6 +1733,18 @@
     <t>Influenza virus B RNA [Presence] in Nasopharynx by NAA with probe detection</t>
   </si>
   <si>
+    <t>76088-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Bronchoalveolar lavage by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>76089-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Nasopharynx by NAA with probe detection</t>
+  </si>
+  <si>
     <t>76626-1</t>
   </si>
   <si>
@@ -1895,6 +1943,12 @@
     <t>Influenza virus B RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>85479-4</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Upper respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>85622-9</t>
   </si>
   <si>
@@ -2087,6 +2141,12 @@
     <t>Measles virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
   </si>
   <si>
+    <t>91133-9</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
     <t>91780-7</t>
   </si>
   <si>
@@ -2121,6 +2181,12 @@
   </si>
   <si>
     <t>Middle East respiratory syndrome coronavirus (MERS-CoV) RNA [Presence] in Lower respiratory specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>92131-2</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus RNA [Presence] in Respiratory system specimen by NAA with probe detection</t>
   </si>
   <si>
     <t>92141-1</t>
@@ -2761,7 +2827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B384"/>
+  <dimension ref="A1:B395"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -5829,15 +5895,103 @@
         <v>792</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -5864,58 +6018,58 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>795</v>
+        <v>817</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>796</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>797</v>
+        <v>819</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>798</v>
+        <v>820</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>800</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>801</v>
+        <v>823</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>802</v>
+        <v>824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>804</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>805</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -5942,98 +6096,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>807</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>809</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>811</v>
+        <v>833</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>813</v>
+        <v>835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>815</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>817</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>819</v>
+        <v>841</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>821</v>
+        <v>843</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>823</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>824</v>
+        <v>846</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>825</v>
+        <v>847</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>826</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-laboratory-observation.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
